--- a/school_counselor_forms/023_general_electives_survey--school_counselor_forms.xlsx
+++ b/school_counselor_forms/023_general_electives_survey--school_counselor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2367,8 +2367,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'art'}</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Art'}</t>
+          <t>Art</t>
         </is>
       </c>
     </row>
@@ -2413,12 +2413,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'music'}</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Music'}</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2464,12 +2464,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -2498,12 +2498,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2515,12 +2515,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'drama'}</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Drama'}</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2532,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'science'}</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Science'}</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'visual_arts'}</t>
+          <t>visual_arts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Visual Arts'}</t>
+          <t>Visual Arts</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'band'}</t>
+          <t>band</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Band'}</t>
+          <t>Band</t>
         </is>
       </c>
     </row>
@@ -2600,12 +2600,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'chorus'}</t>
+          <t>chorus</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Chorus'}</t>
+          <t>Chorus</t>
         </is>
       </c>
     </row>
@@ -2617,12 +2617,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'orchestra'}</t>
+          <t>orchestra</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Orchestra'}</t>
+          <t>Orchestra</t>
         </is>
       </c>
     </row>
@@ -2634,12 +2634,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'sports'}</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Sports'}</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -2651,12 +2651,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'music'}</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Music'}</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -2702,12 +2702,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'choir'}</t>
+          <t>choir</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Choir'}</t>
+          <t>Choir</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2719,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'drama'}</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Drama'}</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
@@ -2736,12 +2736,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'orchestra'}</t>
+          <t>orchestra</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Orchestra'}</t>
+          <t>Orchestra</t>
         </is>
       </c>
     </row>
@@ -2753,12 +2753,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'art'}</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Art'}</t>
+          <t>Art</t>
         </is>
       </c>
     </row>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'band'}</t>
+          <t>band</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Band'}</t>
+          <t>Band</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -2838,12 +2838,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -2855,12 +2855,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'science'}</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Science'}</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
@@ -2872,12 +2872,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -2906,12 +2906,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'music'}</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Music'}</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -2940,12 +2940,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -2957,12 +2957,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'sports'}</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Sports'}</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'chorus'}</t>
+          <t>chorus</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Chorus'}</t>
+          <t>Chorus</t>
         </is>
       </c>
     </row>
@@ -2991,12 +2991,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'band'}</t>
+          <t>band</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'Band'}</t>
+          <t>Band</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'orchestra'}</t>
+          <t>orchestra</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'Orchestra'}</t>
+          <t>Orchestra</t>
         </is>
       </c>
     </row>
@@ -3025,12 +3025,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'drama'}</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'Drama'}</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
@@ -3042,12 +3042,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'choir'}</t>
+          <t>choir</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Choir'}</t>
+          <t>Choir</t>
         </is>
       </c>
     </row>
@@ -3076,12 +3076,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -3093,12 +3093,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'visual_arts'}</t>
+          <t>visual_arts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'Visual Arts'}</t>
+          <t>Visual Arts</t>
         </is>
       </c>
     </row>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3144,12 +3144,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -3178,12 +3178,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -3195,12 +3195,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -3212,12 +3212,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3263,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3280,12 +3280,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'science'}</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'Science'}</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_'music'}</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 'Music'}</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -3331,12 +3331,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'value':_'band'}</t>
+          <t>band</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'value': 'Band'}</t>
+          <t>Band</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'value':_'orchestra'}</t>
+          <t>orchestra</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'value': 'Orchestra'}</t>
+          <t>Orchestra</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3382,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3399,12 +3399,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'value':_'chorus'}</t>
+          <t>chorus</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'value': 'Chorus'}</t>
+          <t>Chorus</t>
         </is>
       </c>
     </row>
@@ -3416,12 +3416,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'value':_'drama'}</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'value': 'Drama'}</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
@@ -3484,12 +3484,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3501,12 +3501,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'value':_'band'}</t>
+          <t>band</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'value': 'Band'}</t>
+          <t>Band</t>
         </is>
       </c>
     </row>
@@ -3535,12 +3535,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'value':_'chorus'}</t>
+          <t>chorus</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'value': 'Chorus'}</t>
+          <t>Chorus</t>
         </is>
       </c>
     </row>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3620,12 +3620,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'value':_'visual_arts'}</t>
+          <t>visual_arts</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'value': 'Visual Arts'}</t>
+          <t>Visual Arts</t>
         </is>
       </c>
     </row>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'value':_'orchestra'}</t>
+          <t>orchestra</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'value': 'Orchestra'}</t>
+          <t>Orchestra</t>
         </is>
       </c>
     </row>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -3671,12 +3671,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'value':_'chorus'}</t>
+          <t>chorus</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'value': 'Chorus'}</t>
+          <t>Chorus</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3705,12 +3705,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -3722,12 +3722,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3756,12 +3756,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'value':_'band'}</t>
+          <t>band</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'value': 'Band'}</t>
+          <t>Band</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3773,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'value':_'visual_arts'}</t>
+          <t>visual_arts</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'value': 'Visual Arts'}</t>
+          <t>Visual Arts</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'value': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3841,12 +3841,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'value':_'drama'}</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'value': 'Drama'}</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
@@ -3858,12 +3858,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -3875,12 +3875,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{'value':_'chorus'}</t>
+          <t>chorus</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'value': 'Chorus'}</t>
+          <t>Chorus</t>
         </is>
       </c>
     </row>
@@ -3943,12 +3943,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3994,12 +3994,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{'value':_'drama'}</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'value': 'Drama'}</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
@@ -4028,12 +4028,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'value': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -4045,12 +4045,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{'value':_'orchestra'}</t>
+          <t>orchestra</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'value': 'Orchestra'}</t>
+          <t>Orchestra</t>
         </is>
       </c>
     </row>
@@ -4062,12 +4062,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -4079,12 +4079,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4096,12 +4096,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -4113,12 +4113,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -4130,12 +4130,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{'value':_'band'}</t>
+          <t>band</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'value': 'Band'}</t>
+          <t>Band</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -4198,12 +4198,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>{'value':_'drama'}</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{'value': 'Drama'}</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
@@ -4266,12 +4266,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{'value': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -4283,12 +4283,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>{'value':_'orchestra'}</t>
+          <t>orchestra</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{'value': 'Orchestra'}</t>
+          <t>Orchestra</t>
         </is>
       </c>
     </row>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>{'value':_'visual_arts'}</t>
+          <t>visual_arts</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{'value': 'Visual Arts'}</t>
+          <t>Visual Arts</t>
         </is>
       </c>
     </row>
@@ -4317,12 +4317,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>{'value':_'chorus'}</t>
+          <t>chorus</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{'value': 'Chorus'}</t>
+          <t>Chorus</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -4351,12 +4351,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -4402,12 +4402,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>{'value':_'band'}</t>
+          <t>band</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>{'value': 'Band'}</t>
+          <t>Band</t>
         </is>
       </c>
     </row>
@@ -4419,12 +4419,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>{'value':_'orchestra'}</t>
+          <t>orchestra</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>{'value': 'Orchestra'}</t>
+          <t>Orchestra</t>
         </is>
       </c>
     </row>
@@ -4504,12 +4504,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -4521,12 +4521,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>{'value':_'chorus'}</t>
+          <t>chorus</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>{'value': 'Chorus'}</t>
+          <t>Chorus</t>
         </is>
       </c>
     </row>
@@ -4538,12 +4538,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -4555,12 +4555,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -4572,12 +4572,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>{'value':_'visual_arts'}</t>
+          <t>visual_arts</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>{'value': 'Visual Arts'}</t>
+          <t>Visual Arts</t>
         </is>
       </c>
     </row>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -4640,12 +4640,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4708,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>{'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>{'value': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>{'value':_'drama'}</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>{'value': 'Drama'}</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -4759,12 +4759,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>{'value':_'visual_arts'}</t>
+          <t>visual_arts</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>{'value': 'Visual Arts'}</t>
+          <t>Visual Arts</t>
         </is>
       </c>
     </row>
@@ -4776,12 +4776,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -4793,12 +4793,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>{'value':_'chorus'}</t>
+          <t>chorus</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>{'value': 'Chorus'}</t>
+          <t>Chorus</t>
         </is>
       </c>
     </row>
@@ -4861,12 +4861,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4912,12 +4912,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -4929,12 +4929,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>{'value':_'orchestra'}</t>
+          <t>orchestra</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>{'value': 'Orchestra'}</t>
+          <t>Orchestra</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4963,12 +4963,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4980,12 +4980,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>{'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>{'value': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -4997,12 +4997,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>{'value':_'drama'}</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>{'value': 'Drama'}</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>{'value':_'visual_arts'}</t>
+          <t>visual_arts</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>{'value': 'Visual Arts'}</t>
+          <t>Visual Arts</t>
         </is>
       </c>
     </row>
@@ -5065,12 +5065,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>{'value':_'chorus'}</t>
+          <t>chorus</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>{'value': 'Chorus'}</t>
+          <t>Chorus</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>{'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>{'value': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>{'value':_'orchestra'}</t>
+          <t>orchestra</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>{'value': 'Orchestra'}</t>
+          <t>Orchestra</t>
         </is>
       </c>
     </row>
@@ -5116,12 +5116,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -5133,12 +5133,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>{'value':_'physical_education'}</t>
+          <t>physical_education</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Education'}</t>
+          <t>Physical Education</t>
         </is>
       </c>
     </row>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>{'value':_'visual_arts'}</t>
+          <t>visual_arts</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>{'value': 'Visual Arts'}</t>
+          <t>Visual Arts</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>{'value':_'band'}</t>
+          <t>band</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>{'value': 'Band'}</t>
+          <t>Band</t>
         </is>
       </c>
     </row>
@@ -5201,12 +5201,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5218,12 +5218,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5235,12 +5235,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -5252,12 +5252,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5269,12 +5269,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>{'value':_'chorus'}</t>
+          <t>chorus</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>{'value': 'Chorus'}</t>
+          <t>Chorus</t>
         </is>
       </c>
     </row>
@@ -5320,12 +5320,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5337,12 +5337,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>{'value':_'orchestra'}</t>
+          <t>orchestra</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>{'value': 'Orchestra'}</t>
+          <t>Orchestra</t>
         </is>
       </c>
     </row>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -5371,12 +5371,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>{'value':_'band'}</t>
+          <t>band</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>{'value': 'Band'}</t>
+          <t>Band</t>
         </is>
       </c>
     </row>
@@ -5388,12 +5388,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>{'value':_'visual_arts'}</t>
+          <t>visual_arts</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>{'value': 'Visual Arts'}</t>
+          <t>Visual Arts</t>
         </is>
       </c>
     </row>
@@ -5405,12 +5405,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>{'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>{'value': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -5422,12 +5422,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5439,12 +5439,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5456,12 +5456,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -5473,12 +5473,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>{'value':_'visual_arts'}</t>
+          <t>visual_arts</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>{'value': 'Visual Arts'}</t>
+          <t>Visual Arts</t>
         </is>
       </c>
     </row>
@@ -5490,12 +5490,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>{'value':_'drama'}</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>{'value': 'Drama'}</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>{'value':_'chorus'}</t>
+          <t>chorus</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>{'value': 'Chorus'}</t>
+          <t>Chorus</t>
         </is>
       </c>
     </row>
@@ -5558,12 +5558,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5575,12 +5575,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5592,12 +5592,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5609,12 +5609,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>{'value':_'orchestra'}</t>
+          <t>orchestra</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>{'value': 'Orchestra'}</t>
+          <t>Orchestra</t>
         </is>
       </c>
     </row>
@@ -5626,12 +5626,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>{'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>{'value': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -5643,12 +5643,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5660,12 +5660,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>{'value':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>{'value': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -5677,12 +5677,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -5694,12 +5694,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>{'value':_'chorus'}</t>
+          <t>chorus</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>{'value': 'Chorus'}</t>
+          <t>Chorus</t>
         </is>
       </c>
     </row>
@@ -5711,12 +5711,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>{'value':_'drama'}</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>{'value': 'Drama'}</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
